--- a/docs/Mapping_casi_uso/cittadinanza/Citt_020.xlsx
+++ b/docs/Mapping_casi_uso/cittadinanza/Citt_020.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="143">
   <si>
     <t>Sezione</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Allegati</t>
   </si>
   <si>
-    <t>Decreto del Tribunale</t>
+    <t>Copia dell'atto di cittadinanza che contiene l'esito di accertamento rilasciato dal consolato</t>
   </si>
   <si>
     <t>SI</t>
@@ -47,12 +47,12 @@
     <t/>
   </si>
   <si>
-    <t>Copia integrale dell'atto di cittadinanza dell'interessato</t>
-  </si>
-  <si>
     <t>Copia integrale dell'atto di nascita dell'interessato</t>
   </si>
   <si>
+    <t>NO</t>
+  </si>
+  <si>
     <t>Formula</t>
   </si>
   <si>
@@ -125,9 +125,6 @@
     <t>Cognome</t>
   </si>
   <si>
-    <t>NO</t>
-  </si>
-  <si>
     <t>evento.intestatari[0]</t>
   </si>
   <si>
@@ -308,6 +305,12 @@
     <t>flagFirmatario</t>
   </si>
   <si>
+    <t>Residenza al momento dell'evento originario</t>
+  </si>
+  <si>
+    <t>residenzaOriginaria</t>
+  </si>
+  <si>
     <t>Ulteriore cittadinanza di cui è in possesso</t>
   </si>
   <si>
@@ -426,30 +429,6 @@
   </si>
   <si>
     <t>nomeNazioneEnte</t>
-  </si>
-  <si>
-    <t>Provincia ente</t>
-  </si>
-  <si>
-    <t>idProvinciaEnte</t>
-  </si>
-  <si>
-    <t>Provincia ente - Descrizione</t>
-  </si>
-  <si>
-    <t>siglaProvinciaEnte</t>
-  </si>
-  <si>
-    <t>Comune ente</t>
-  </si>
-  <si>
-    <t>idComuneEnte</t>
-  </si>
-  <si>
-    <t>Comune ente - Descrizione</t>
-  </si>
-  <si>
-    <t>nomeComuneEnte</t>
   </si>
   <si>
     <t>Anagrafica Consolato</t>
@@ -520,11 +499,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.59765625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="50.296875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="81.5703125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.5625" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="43.9609375" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="25.734375" customWidth="true" bestFit="true"/>
@@ -586,7 +565,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>10</v>
@@ -603,10 +582,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>9</v>
@@ -625,49 +604,49 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>10</v>
+      <c r="A5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>15</v>
+      <c r="A6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -675,7 +654,7 @@
         <v>16</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>9</v>
@@ -684,7 +663,7 @@
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>10</v>
@@ -698,7 +677,7 @@
         <v>16</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>9</v>
@@ -707,7 +686,7 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>10</v>
@@ -721,7 +700,7 @@
         <v>16</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>9</v>
@@ -730,7 +709,7 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>10</v>
@@ -741,19 +720,19 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>10</v>
@@ -767,7 +746,7 @@
         <v>27</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>9</v>
@@ -776,7 +755,7 @@
         <v>29</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>10</v>
@@ -790,7 +769,7 @@
         <v>27</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>9</v>
@@ -799,7 +778,7 @@
         <v>29</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>10</v>
@@ -810,19 +789,19 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>10</v>
@@ -836,16 +815,16 @@
         <v>35</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>10</v>
@@ -859,16 +838,16 @@
         <v>35</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>10</v>
@@ -882,16 +861,16 @@
         <v>35</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>10</v>
@@ -905,16 +884,16 @@
         <v>35</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>10</v>
@@ -928,16 +907,16 @@
         <v>35</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>10</v>
@@ -951,16 +930,16 @@
         <v>35</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>10</v>
@@ -974,16 +953,16 @@
         <v>35</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>10</v>
@@ -997,16 +976,16 @@
         <v>35</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>10</v>
@@ -1020,16 +999,16 @@
         <v>35</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>10</v>
@@ -1043,16 +1022,16 @@
         <v>35</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>10</v>
@@ -1066,16 +1045,16 @@
         <v>35</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>10</v>
@@ -1089,16 +1068,16 @@
         <v>35</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>10</v>
@@ -1112,16 +1091,16 @@
         <v>35</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>10</v>
@@ -1135,16 +1114,16 @@
         <v>35</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>10</v>
@@ -1158,16 +1137,16 @@
         <v>35</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>10</v>
@@ -1181,16 +1160,16 @@
         <v>35</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>10</v>
@@ -1204,16 +1183,16 @@
         <v>35</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>10</v>
@@ -1227,16 +1206,16 @@
         <v>35</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>10</v>
@@ -1250,16 +1229,16 @@
         <v>35</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>10</v>
@@ -1273,16 +1252,16 @@
         <v>35</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>10</v>
@@ -1296,16 +1275,16 @@
         <v>35</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>10</v>
@@ -1319,16 +1298,16 @@
         <v>35</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>10</v>
@@ -1342,16 +1321,16 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>10</v>
@@ -1365,16 +1344,16 @@
         <v>35</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>10</v>
@@ -1388,16 +1367,16 @@
         <v>35</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>10</v>
@@ -1411,16 +1390,16 @@
         <v>35</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>10</v>
@@ -1434,16 +1413,16 @@
         <v>35</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>10</v>
@@ -1457,16 +1436,16 @@
         <v>35</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>10</v>
@@ -1480,16 +1459,16 @@
         <v>35</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>10</v>
@@ -1503,16 +1482,16 @@
         <v>35</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>10</v>
@@ -1526,7 +1505,7 @@
         <v>35</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>9</v>
@@ -1535,7 +1514,7 @@
         <v>29</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>10</v>
@@ -1549,7 +1528,7 @@
         <v>35</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>9</v>
@@ -1558,7 +1537,7 @@
         <v>29</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>10</v>
@@ -1569,131 +1548,131 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B47" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G47" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>19</v>
@@ -1702,44 +1681,44 @@
         <v>10</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>22</v>
@@ -1748,116 +1727,116 @@
         <v>10</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>10</v>
@@ -1868,19 +1847,19 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>10</v>
@@ -1891,19 +1870,19 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>10</v>
@@ -1914,19 +1893,19 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>10</v>
@@ -1937,19 +1916,19 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>10</v>
@@ -1960,19 +1939,19 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>10</v>
@@ -1983,116 +1962,24 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G65" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G66" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="F67" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G67" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G68" s="2" t="s">
         <v>20</v>
       </c>
     </row>
